--- a/Data/Rules/Canine Caviar Rules Matrix.xlsx
+++ b/Data/Rules/Canine Caviar Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="114">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>14972</t>
@@ -684,10 +687,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN37"/>
+  <dimension ref="A1:AO37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -808,16 +811,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -930,16 +936,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>22</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1052,16 +1061,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>35</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1174,16 +1186,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>37</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1296,16 +1311,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>27</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1418,16 +1436,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>24</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1540,16 +1561,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>4</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1662,16 +1686,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>8</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1784,16 +1811,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>4</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1906,16 +1936,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>8</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2028,16 +2061,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>7</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2150,16 +2186,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2272,16 +2311,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>9</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2394,16 +2436,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2516,16 +2561,19 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>10</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2638,16 +2686,19 @@
       <c r="AN16">
         <v>0</v>
       </c>
+      <c r="AO16">
+        <v>13</v>
+      </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2760,16 +2811,19 @@
       <c r="AN17">
         <v>0</v>
       </c>
+      <c r="AO17">
+        <v>5</v>
+      </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2882,16 +2936,19 @@
       <c r="AN18">
         <v>0</v>
       </c>
+      <c r="AO18">
+        <v>9</v>
+      </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3004,16 +3061,19 @@
       <c r="AN19">
         <v>0</v>
       </c>
+      <c r="AO19">
+        <v>11</v>
+      </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3126,16 +3186,19 @@
       <c r="AN20">
         <v>0</v>
       </c>
+      <c r="AO20">
+        <v>12</v>
+      </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C21" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3248,16 +3311,19 @@
       <c r="AN21">
         <v>0</v>
       </c>
+      <c r="AO21">
+        <v>15</v>
+      </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3370,16 +3436,19 @@
       <c r="AN22">
         <v>0</v>
       </c>
+      <c r="AO22">
+        <v>15</v>
+      </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3492,16 +3561,19 @@
       <c r="AN23">
         <v>0</v>
       </c>
+      <c r="AO23">
+        <v>13</v>
+      </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3614,16 +3686,19 @@
       <c r="AN24">
         <v>0</v>
       </c>
+      <c r="AO24">
+        <v>19</v>
+      </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3736,16 +3811,19 @@
       <c r="AN25">
         <v>0</v>
       </c>
+      <c r="AO25">
+        <v>15</v>
+      </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3858,16 +3936,19 @@
       <c r="AN26">
         <v>0</v>
       </c>
+      <c r="AO26">
+        <v>14</v>
+      </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3980,16 +4061,19 @@
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>10</v>
+      </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4102,16 +4186,19 @@
       <c r="AN28">
         <v>0</v>
       </c>
+      <c r="AO28">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4224,16 +4311,19 @@
       <c r="AN29">
         <v>0</v>
       </c>
+      <c r="AO29">
+        <v>7</v>
+      </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:41">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4346,16 +4436,19 @@
       <c r="AN30">
         <v>0</v>
       </c>
+      <c r="AO30">
+        <v>12</v>
+      </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4468,16 +4561,19 @@
       <c r="AN31">
         <v>0</v>
       </c>
+      <c r="AO31">
+        <v>13</v>
+      </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C32" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4590,16 +4686,19 @@
       <c r="AN32">
         <v>0</v>
       </c>
+      <c r="AO32">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4712,16 +4811,19 @@
       <c r="AN33">
         <v>0</v>
       </c>
+      <c r="AO33">
+        <v>11</v>
+      </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -4834,16 +4936,19 @@
       <c r="AN34">
         <v>0</v>
       </c>
+      <c r="AO34">
+        <v>11</v>
+      </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:41">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -4956,16 +5061,19 @@
       <c r="AN35">
         <v>0</v>
       </c>
+      <c r="AO35">
+        <v>9</v>
+      </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:41">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5078,16 +5186,19 @@
       <c r="AN36">
         <v>0</v>
       </c>
+      <c r="AO36">
+        <v>11</v>
+      </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:41">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5199,6 +5310,9 @@
       </c>
       <c r="AN37">
         <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
